--- a/artfynd/A 24755-2024 artfynd.xlsx
+++ b/artfynd/A 24755-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105160080</v>
+        <v>105160056</v>
       </c>
       <c r="B2" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>256703</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597875.9109864413</v>
+        <v>597921</v>
       </c>
       <c r="R2" t="n">
-        <v>7032375.063969155</v>
+        <v>7031949</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,33 +743,17 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Luktar starkt av läder</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105160061</v>
+        <v>105160062</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597771.0744112714</v>
+        <v>597859</v>
       </c>
       <c r="R3" t="n">
-        <v>7031956.669902273</v>
+        <v>7031976</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,24 +844,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105160084</v>
+        <v>105160074</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597879.0934560215</v>
+        <v>597950</v>
       </c>
       <c r="R4" t="n">
-        <v>7032579.149000001</v>
+        <v>7032284</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -991,19 +945,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105160087</v>
+        <v>105160082</v>
       </c>
       <c r="B5" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598043.668150873</v>
+        <v>597880</v>
       </c>
       <c r="R5" t="n">
-        <v>7032789.957791604</v>
+        <v>7032522</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1107,19 +1046,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105160083</v>
+        <v>105160089</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597890.0492620409</v>
+        <v>598161</v>
       </c>
       <c r="R6" t="n">
-        <v>7032573.207937479</v>
+        <v>7032889</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,24 +1147,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105160077</v>
+        <v>105160055</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597926.3399252489</v>
+        <v>597921</v>
       </c>
       <c r="R7" t="n">
-        <v>7032311.597610073</v>
+        <v>7031949</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,19 +1248,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105160081</v>
+        <v>105160079</v>
       </c>
       <c r="B8" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597871.6275757801</v>
+        <v>597921</v>
       </c>
       <c r="R8" t="n">
-        <v>7032383.00299212</v>
+        <v>7032312</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1460,19 +1349,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105160057</v>
+        <v>105160086</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1543,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597883.7920180773</v>
+        <v>597999</v>
       </c>
       <c r="R9" t="n">
-        <v>7031956.081057076</v>
+        <v>7032770</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1576,19 +1450,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105160086</v>
+        <v>105160075</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597998.9219809122</v>
+        <v>597950</v>
       </c>
       <c r="R10" t="n">
-        <v>7032770.655028464</v>
+        <v>7032284</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1692,19 +1551,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105160060</v>
+        <v>105160087</v>
       </c>
       <c r="B11" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1775,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597735.8233866427</v>
+        <v>598043</v>
       </c>
       <c r="R11" t="n">
-        <v>7031905.372067994</v>
+        <v>7032790</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,19 +1652,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105160079</v>
+        <v>105160076</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1891,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597920.5089929374</v>
+        <v>597938</v>
       </c>
       <c r="R12" t="n">
-        <v>7032311.419109756</v>
+        <v>7032305</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,19 +1753,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105160058</v>
+        <v>105160077</v>
       </c>
       <c r="B13" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1983,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2007,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597771.6663098211</v>
+        <v>597927</v>
       </c>
       <c r="R13" t="n">
-        <v>7031922.609710098</v>
+        <v>7032311</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2040,19 +1854,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,37 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105160062</v>
+        <v>105160054</v>
       </c>
       <c r="B14" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2123,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597858.9381971821</v>
+        <v>597922</v>
       </c>
       <c r="R14" t="n">
-        <v>7031975.94692583</v>
+        <v>7031939</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2156,19 +1955,9 @@
           <t>2022-09-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,6 +1981,936 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105160083</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>597890</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7032573</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>105160088</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>598132</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7032860</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>105160061</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>597771</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7031957</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>105160058</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>597771</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7031923</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>105160081</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>597871</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7032383</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>105160057</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>597884</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7031956</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>105160060</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>597736</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7031905</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>105160084</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>597879</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7032579</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>105160080</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>597876</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7032375</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-09-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Luktar starkt av läder</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>

--- a/artfynd/A 24755-2024 artfynd.xlsx
+++ b/artfynd/A 24755-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160056</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160062</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160074</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160082</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160089</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160055</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160079</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160086</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160075</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160087</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160076</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160077</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160054</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160083</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160088</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2303,6 +2383,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160061</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,6 +2489,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160058</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2505,6 +2595,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160081</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2606,6 +2701,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160057</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2707,6 +2807,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160060</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2808,6 +2913,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160084</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2915,8 +3025,37 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160080</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>